--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:02</t>
+    <t xml:space="preserve">2026-09-24 01:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -552,7 +552,7 @@
         <v>-0.04</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
         <v>-0.09</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +580,7 @@
         <v>-0.04</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -594,7 +594,7 @@
         <v>0.1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         <v>0.08</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -773,10 +773,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -790,7 +790,7 @@
         <v>-0.54</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -804,7 +804,7 @@
         <v>-0.33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -815,10 +815,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -829,10 +829,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -846,7 +846,7 @@
         <v>0.06</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -874,7 +874,7 @@
         <v>-0.01</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -888,7 +888,7 @@
         <v>-0.53</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:51</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
